--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,48 +791,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133856930</v>
+        <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99195</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knaften, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679623</v>
+        <v>679573</v>
       </c>
       <c r="R3" t="n">
-        <v>7152789</v>
+        <v>7152520</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -892,62 +906,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133856930</t>
+          <t>https://artportalen.se/Sighting/137282925</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121062024</v>
+        <v>133856930</v>
       </c>
       <c r="B4" t="n">
-        <v>97977</v>
+        <v>99195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1,5 km SO om Gravsjö, Ly lm</t>
+          <t>Knaften, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679590</v>
+        <v>679623</v>
       </c>
       <c r="R4" t="n">
-        <v>7152763</v>
+        <v>7152789</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,17 +977,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>i kanten av nerskuret dike, foto men inget belägg</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,31 +996,30 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121062024</t>
+          <t>https://artportalen.se/Sighting/133856930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128649125</v>
+        <v>121062024</v>
       </c>
       <c r="B5" t="n">
         <v>97977</v>
@@ -1038,24 +1043,32 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SO om Gravsjö, Ly lm</t>
+          <t>1,5 km SO om Gravsjö, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679566</v>
+        <v>679590</v>
       </c>
       <c r="R5" t="n">
-        <v>7152712</v>
+        <v>7152763</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1092,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>i kanten av nerskuret dike, foto men inget belägg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,11 +1123,114 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonas F Grahn, Henrik Sporrong</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128649125</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SO om Gravsjö, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>679566</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7152712</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn, Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128649125</t>
         </is>
@@ -1121,6 +1242,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56566-2025 artfynd.xlsx
+++ b/artfynd/A 56566-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137282925</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
